--- a/base_mvi_precessada.xlsx
+++ b/base_mvi_precessada.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Estado </t>
+          <t>Estado</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -434,17 +434,17 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gini </t>
+          <t>Gini</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Desmprego Médio 2024</t>
+          <t>Desemprego Médio 2024</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Cluster Matemático</t>
+          <t>Score Desenvolvimento</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
@@ -472,11 +472,11 @@
         <v>0.5740181268882174</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0.3907747549708871</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Intermediario</t>
+          <t>Intermediário</t>
         </is>
       </c>
     </row>
@@ -499,11 +499,11 @@
         <v>0.6706948640483381</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>0.2407610748976433</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Desenvolvido</t>
+          <t>Vulnerável</t>
         </is>
       </c>
     </row>
@@ -526,11 +526,11 @@
         <v>0.7552870090634438</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>0.1885302999911345</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Desenvolvido</t>
+          <t>Vulnerável</t>
         </is>
       </c>
     </row>
@@ -553,11 +553,11 @@
         <v>0.6797583081570995</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>0.372807109715832</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Desenvolvido</t>
+          <t>Intermediário</t>
         </is>
       </c>
     </row>
@@ -580,11 +580,11 @@
         <v>0.9939577039274923</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>0.2116972553825447</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Desenvolvido</t>
+          <t>Vulnerável</t>
         </is>
       </c>
     </row>
@@ -607,11 +607,11 @@
         <v>0.5317220543806644</v>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>0.3119654584175294</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Desenvolvido</t>
+          <t>Vulnerável</t>
         </is>
       </c>
     </row>
@@ -634,11 +634,11 @@
         <v>0.7703927492447127</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>0.5522662953941392</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Intermediario</t>
+          <t>Intermediário</t>
         </is>
       </c>
     </row>
@@ -661,11 +661,11 @@
         <v>0.2024169184290029</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>0.5952794618359539</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Vulneravel</t>
+          <t>Intermediário</t>
         </is>
       </c>
     </row>
@@ -688,11 +688,11 @@
         <v>0.2900302114803623</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>0.6451872367678246</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Vulneravel</t>
+          <t>Intermediário</t>
         </is>
       </c>
     </row>
@@ -715,11 +715,11 @@
         <v>0.5589123867069484</v>
       </c>
       <c r="F11" t="n">
-        <v>2</v>
+        <v>0.3381450640977845</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Desenvolvido</t>
+          <t>Intermediário</t>
         </is>
       </c>
     </row>
@@ -742,11 +742,11 @@
         <v>0.003021148036253696</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>0.7039653106260556</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Vulneravel</t>
+          <t>Desenvolvido</t>
         </is>
       </c>
     </row>
@@ -769,11 +769,11 @@
         <v>0.1238670694864049</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>0.711417792173584</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Vulneravel</t>
+          <t>Desenvolvido</t>
         </is>
       </c>
     </row>
@@ -796,11 +796,11 @@
         <v>0.2749244712990936</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>0.6957321980151649</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Vulneravel</t>
+          <t>Desenvolvido</t>
         </is>
       </c>
     </row>
@@ -823,11 +823,11 @@
         <v>0.5498489425981872</v>
       </c>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>0.3677533753825982</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Desenvolvido</t>
+          <t>Intermediário</t>
         </is>
       </c>
     </row>
@@ -850,11 +850,11 @@
         <v>0.6978851963746222</v>
       </c>
       <c r="F16" t="n">
-        <v>2</v>
+        <v>0.3508440886988385</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Desenvolvido</t>
+          <t>Intermediário</t>
         </is>
       </c>
     </row>
@@ -877,11 +877,11 @@
         <v>0.1389728096676736</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>0.7027750168889519</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Vulneravel</t>
+          <t>Desenvolvido</t>
         </is>
       </c>
     </row>
@@ -904,11 +904,11 @@
         <v>0.9999999999999998</v>
       </c>
       <c r="F18" t="n">
-        <v>2</v>
+        <v>0.1362270934777636</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Desenvolvido</t>
+          <t>Vulnerável</t>
         </is>
       </c>
     </row>
@@ -931,11 +931,11 @@
         <v>0.6435045317220542</v>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>0.401207449220543</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Intermediario</t>
+          <t>Intermediário</t>
         </is>
       </c>
     </row>
@@ -958,11 +958,11 @@
         <v>0.7552870090634438</v>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>0.4193296803372606</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Intermediario</t>
+          <t>Intermediário</t>
         </is>
       </c>
     </row>
@@ -985,11 +985,11 @@
         <v>0.7492447129909361</v>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
+        <v>0.3146357295555086</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Intermediario</t>
+          <t>Vulnerável</t>
         </is>
       </c>
     </row>
@@ -1012,11 +1012,11 @@
         <v>0.2870090634441086</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>0.733661138991887</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Vulneravel</t>
+          <t>Desenvolvido</t>
         </is>
       </c>
     </row>
@@ -1039,11 +1039,11 @@
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>0.6708029645465774</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Vulneravel</t>
+          <t>Desenvolvido</t>
         </is>
       </c>
     </row>
@@ -1066,11 +1066,11 @@
         <v>0.4773413897280966</v>
       </c>
       <c r="F24" t="n">
-        <v>1</v>
+        <v>0.3953068582962231</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Intermediario</t>
+          <t>Intermediário</t>
         </is>
       </c>
     </row>
@@ -1093,11 +1093,11 @@
         <v>0.02416918429003012</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>0.9026105516836416</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Vulneravel</t>
+          <t>Desenvolvido</t>
         </is>
       </c>
     </row>
@@ -1120,11 +1120,11 @@
         <v>0.4229607250755285</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>0.6855974418177904</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Vulneravel</t>
+          <t>Desenvolvido</t>
         </is>
       </c>
     </row>
@@ -1147,11 +1147,11 @@
         <v>0.7311178247734136</v>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
+        <v>0.3647446849198781</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Intermediario</t>
+          <t>Intermediário</t>
         </is>
       </c>
     </row>
@@ -1174,11 +1174,11 @@
         <v>0.2658610271903321</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>0.5741488456211171</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Vulneravel</t>
+          <t>Intermediário</t>
         </is>
       </c>
     </row>
